--- a/files/telco_b2b_monitor.xlsx
+++ b/files/telco_b2b_monitor.xlsx
@@ -1090,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2140,6 +2140,561 @@
         </is>
       </c>
       <c r="G29" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="19" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>WindTre Business</t>
+        </is>
+      </c>
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>WindTre e Google One: partnership per AI e archiviazione cloud</t>
+        </is>
+      </c>
+      <c r="D30" s="19" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E30" s="19" t="inlineStr">
+        <is>
+          <t>WindTre annuncia la partnership con Google One, il servizio in abbonamento di Google che offre spazio di archiviazione cloud e funzioni basate sull'Intelligenza Artificiale. Gli utenti potranno accedere a soluzioni digitali evolute (archivio foto, Gmail, Drive) e, in alcuni piani, a modelli e funzionalità avanzate AI di Google, attivabili tramite area personale su sito e App.</t>
+        </is>
+      </c>
+      <c r="F30" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G30" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="19" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone</t>
+        </is>
+      </c>
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>Fastweb + Vodafone e Istat nel progetto Multi-MNO: dati rete mobile per statistiche europee</t>
+        </is>
+      </c>
+      <c r="D31" s="19" t="inlineStr">
+        <is>
+          <t>Mobile Analytics</t>
+        </is>
+      </c>
+      <c r="E31" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb + Vodafone partecipa alla sperimentazione Multi-MNO con Istat (progetto europeo MNO-MINDS co-finanziato da Eurostat) per sviluppare uno standard per l'elaborazione di dati degli operatori di rete mobile a fini statistici. Il progetto integra dati MNO per produrre statistiche ufficiali su spostamenti e dinamiche territoriali.</t>
+        </is>
+      </c>
+      <c r="F31" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G31" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="19" t="inlineStr">
+        <is>
+          <t>18/03/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="19" t="inlineStr">
+        <is>
+          <t>Retelit</t>
+        </is>
+      </c>
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>Retelit Datacenter ottiene finanziamento da 375 milioni di euro per espansione data center in Italia</t>
+        </is>
+      </c>
+      <c r="D32" s="19" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E32" s="19" t="inlineStr">
+        <is>
+          <t>Retelit Datacenter, piattaforma data center del Gruppo Retelit controllata da Asterion Industrial Partners, ha ottenuto un finanziamento complessivo da 375 milioni di euro. Generali Investments (Infranity) ha contribuito con 175 milioni a supporto dell'espansione dell'infrastruttura cloud e data center in Italia.</t>
+        </is>
+      </c>
+      <c r="F32" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G32" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="19" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="19" t="inlineStr">
+        <is>
+          <t>TIM Enterprise</t>
+        </is>
+      </c>
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>RAN sharing 5G, l'accordo Tim-Fastweb+Vodafone aumenta il reach e il vantaggio competitivo</t>
+        </is>
+      </c>
+      <c r="D33" s="19" t="inlineStr">
+        <is>
+          <t>Mobile Private Networks</t>
+        </is>
+      </c>
+      <c r="E33" s="19" t="inlineStr">
+        <is>
+          <t>Il report Opensignal analizza gli effetti immediati del RAN sharing 5G tra TIM e Fastweb+Vodafone annunciato a gennaio 2026: miglioramenti nella copertura rurale 5G, qualità di rete per i clienti mobili e posizionamento in vista del rinnovo licenze spettro radio 2029.</t>
+        </is>
+      </c>
+      <c r="F33" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G33" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="36" customHeight="1">
+      <c r="A34" s="19" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone</t>
+        </is>
+      </c>
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>RAN sharing 5G, l'accordo Tim-Fastweb+Vodafone aumenta il reach e il vantaggio competitivo</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>Mobile Private Networks</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>Opensignal certifica i benefici immediati del RAN sharing 5G tra Fastweb+Vodafone e TIM: espansione 5G nelle aree rurali, miglioramenti misurabili nell'esperienza utente e rafforzamento competitivo per il 2029.</t>
+        </is>
+      </c>
+      <c r="F34" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G34" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="36" customHeight="1">
+      <c r="A35" s="19" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone</t>
+        </is>
+      </c>
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>MNO-Minds: Istat e Fastweb+Vodafone definiscono nuove metodologie europee per Mobile Analytics</t>
+        </is>
+      </c>
+      <c r="D35" s="19" t="inlineStr">
+        <is>
+          <t>Mobile Analytics</t>
+        </is>
+      </c>
+      <c r="E35" s="19" t="inlineStr">
+        <is>
+          <t>Concluso il progetto europeo MNO-Minds (co-finanziato da Eurostat) di cui Istat è capofila: Fastweb+Vodafone ha fornito dati di rete mobile anonimizzati per nuove metodologie statistiche su spostamenti e presenze territoriali, base per un futuro dialogo strutturato tra operatori telco e istituti nazionali di statistica.</t>
+        </is>
+      </c>
+      <c r="F35" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G35" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="36" customHeight="1">
+      <c r="A36" s="19" t="inlineStr">
+        <is>
+          <t>19/03/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="19" t="inlineStr">
+        <is>
+          <t>Aruba S.p.A.</t>
+        </is>
+      </c>
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>CISPE: Aruba tra i firmatari della lettera aperta per un Cloud Act europeo sovrano</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>Il CEO di Aruba Stefano Cecconi firma insieme a 24 altri CEO di cloud provider europei la lettera aperta a CISPE sul futuro Cloud and AI Development Act (CADA) UE, chiedendo requisiti stringenti di sovranità digitale per proteggere le infrastrutture cloud critiche europee.</t>
+        </is>
+      </c>
+      <c r="F36" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G36" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="19" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="19" t="inlineStr">
+        <is>
+          <t>TIM Enterprise</t>
+        </is>
+      </c>
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>Sovranità cloud e AI, fondamenta della nuova autonomia digitale</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>L'intelligenza artificiale entra nella fase produttiva e costringe imprese e PA a guardare oltre modelli e funzionalità. La vera partita si gioca sotto il livello applicativo: infrastrutture, governance del dato, compliance e libertà di evoluzione.</t>
+        </is>
+      </c>
+      <c r="F37" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G37" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="36" customHeight="1">
+      <c r="A38" s="19" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="19" t="inlineStr">
+        <is>
+          <t>TIM Enterprise</t>
+        </is>
+      </c>
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>Accordo TIM e Fastweb+Vodafone per costruzione nuove torri 5G in Italia</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>Mobile Private Networks</t>
+        </is>
+      </c>
+      <c r="E38" s="19" t="inlineStr">
+        <is>
+          <t>TIM e Fastweb+Vodafone operano come anchor tenant per la costruzione di nuove torri 5G con piano di sviluppo pluriennale, puntando a migliorare efficienza operativa e allineare i costi alla media europea mantenendo alti standard infrastrutturali.</t>
+        </is>
+      </c>
+      <c r="F38" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G38" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="36" customHeight="1">
+      <c r="A39" s="19" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone</t>
+        </is>
+      </c>
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone e TIM: accordo per sviluppo condiviso torri e rete 5G</t>
+        </is>
+      </c>
+      <c r="D39" s="19" t="inlineStr">
+        <is>
+          <t>Mobile Private Networks</t>
+        </is>
+      </c>
+      <c r="E39" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone e TIM siglano un'alleanza strategica per la costruzione e condivisione di nuove torri 5G in Italia. L'accordo, annunciato il 19 marzo 2026, prevede ruolo da anchor tenant per entrambi gli operatori con contratti di lungo periodo a condizioni di mercato.</t>
+        </is>
+      </c>
+      <c r="F39" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G39" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>WindTre Business</t>
+        </is>
+      </c>
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>Gruppo Codognotto affida la cybersecurity a WindTre Business</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E40" s="19" t="inlineStr">
+        <is>
+          <t>Il Gruppo Codognotto, azienda italiana della logistica con 30 sedi in 16 Paesi e circa 250.000 trasporti/anno, ha scelto WindTre Business per elevare il proprio livello di cybersecurity e protezione digitale, assicurando continuità ai servizi erogati a clienti e partner internazionali.</t>
+        </is>
+      </c>
+      <c r="F40" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G40" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="36" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="19" t="inlineStr">
+        <is>
+          <t>Retelit</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>Wasabi e Retelit trasformano i servizi di cloud object storage in Italia</t>
+        </is>
+      </c>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E41" s="19" t="inlineStr">
+        <is>
+          <t>Retelit, top B2B telco e provider di servizi digitali in Italia, fa squadra con Wasabi per offrire ai propri clienti soluzioni di cloud storage scalabili, cost-effective e cyber-resilient su tutto il territorio italiano.</t>
+        </is>
+      </c>
+      <c r="F41" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G41" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="36" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="19" t="inlineStr">
+        <is>
+          <t>Retelit</t>
+        </is>
+      </c>
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>UniCredit e ING coordinano finanziamento da 375M€ a Retelit per espansione datacenter</t>
+        </is>
+      </c>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E42" s="19" t="inlineStr">
+        <is>
+          <t>Retelit Datacenter ottiene un finanziamento da 375 milioni di euro, con UniCredit e ING come Global Coordinator, destinato all'espansione della piattaforma nazionale per l'interconnessione dei datacenter. Retelit punta a consolidare servizi di connettività, cloud, co-location e interconnessione per imprese, PA e operatori.</t>
+        </is>
+      </c>
+      <c r="F42" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G42" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="36" customHeight="1">
+      <c r="A43" s="19" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="19" t="inlineStr">
+        <is>
+          <t>Tessellis/Tiscali</t>
+        </is>
+      </c>
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>Tessellis-Canarbino: accordo per ramo B2C Tiscali e Linkem, avviati 180 licenziamenti collettivi</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Generale</t>
+        </is>
+      </c>
+      <c r="E43" s="19" t="inlineStr">
+        <is>
+          <t>Il CdA di Tessellis ha accettato l'offerta vincolante di Canarbino per il ramo B2C di Tiscali e Linkem: contratto di affitto di 12 mesi dal 1° giugno 2026 con opzione di acquisizione. Contestualmente avviati 180 licenziamenti collettivi (su 729 dipendenti) come condizione dell'accordo. Il ramo B2B rimane in Tessellis.</t>
+        </is>
+      </c>
+      <c r="F43" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G43" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="36" customHeight="1">
+      <c r="A44" s="19" t="inlineStr">
+        <is>
+          <t>20/03/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="19" t="inlineStr">
+        <is>
+          <t>Aruba S.p.A.</t>
+        </is>
+      </c>
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>Nuova promo Aruba Hosting: piani WordPress con strumenti AI integrati</t>
+        </is>
+      </c>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>SaaS</t>
+        </is>
+      </c>
+      <c r="E44" s="19" t="inlineStr">
+        <is>
+          <t>Aruba lancia una nuova promozione sui piani Hosting con WordPress preinstallato e strumenti AI integrati per PMI e professionisti. I prezzi partono da 11,90 euro per il primo anno, con focus su semplicità di gestione e funzionalità avanzate.</t>
+        </is>
+      </c>
+      <c r="F44" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G44" s="19" t="inlineStr">
         <is>
           <t>🆕 Sì</t>
         </is>
@@ -2177,6 +2732,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F27" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F28" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F29" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F30" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F31" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F32" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F33" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F34" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F35" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F36" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F37" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F38" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F39" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F40" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F41" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId42"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/files/telco_b2b_monitor.xlsx
+++ b/files/telco_b2b_monitor.xlsx
@@ -1090,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2695,6 +2695,191 @@
         </is>
       </c>
       <c r="G44" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="36" customHeight="1">
+      <c r="A45" s="19" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="19" t="inlineStr">
+        <is>
+          <t>TIM Enterprise</t>
+        </is>
+      </c>
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>Del Fante: Avanti su cloud sovrano. Tim resterà standalone</t>
+        </is>
+      </c>
+      <c r="D45" s="19" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E45" s="19" t="inlineStr">
+        <is>
+          <t>Poste presenta offerta su Tim come mossa strategica per cloud sovrano e dati. Del Fante annuncia sinergie da 700 milioni e indipendenza operativa.</t>
+        </is>
+      </c>
+      <c r="F45" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G45" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="36" customHeight="1">
+      <c r="A46" s="19" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="19" t="inlineStr">
+        <is>
+          <t>TIM Enterprise</t>
+        </is>
+      </c>
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>Poste punta all intero capitale di Tim: operazione da 10,8 miliardi</t>
+        </is>
+      </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>Generale</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>Poste Italiane avanza offerta sistemica su TIM per convergenza reti, cloud, edge-computing, dati e identità digitale, aprendo nuove opportunità B2B.</t>
+        </is>
+      </c>
+      <c r="F46" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G46" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="36" customHeight="1">
+      <c r="A47" s="19" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="19" t="inlineStr">
+        <is>
+          <t>WindTre Business</t>
+        </is>
+      </c>
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>Gruppo Codognotto potenzia la cybersecurity con WINDTRE BUSINESS</t>
+        </is>
+      </c>
+      <c r="D47" s="19" t="inlineStr">
+        <is>
+          <t>Cybersecurity</t>
+        </is>
+      </c>
+      <c r="E47" s="19" t="inlineStr">
+        <is>
+          <t>WindTre Business porta il proprio servizio MDR basato su CrowdStrike e AI nel settore logistica: SOC attivo 24/7 tramite RAD, azienda controllata WindTre.</t>
+        </is>
+      </c>
+      <c r="F47" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G47" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="36" customHeight="1">
+      <c r="A48" s="19" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="19" t="inlineStr">
+        <is>
+          <t>Retelit</t>
+        </is>
+      </c>
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>Retelit: finanziamento da 375 milioni per espansione piattaforma datacenter nazionale</t>
+        </is>
+      </c>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E48" s="19" t="inlineStr">
+        <is>
+          <t>UniCredit e ING Global Coordinator per prestito a Retelit Datacenter destinato a espandere la piattaforma di interconnessione datacenter per cloud, co-location e connettività B2B.</t>
+        </is>
+      </c>
+      <c r="F48" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G48" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="36" customHeight="1">
+      <c r="A49" s="19" t="inlineStr">
+        <is>
+          <t>24/03/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="19" t="inlineStr">
+        <is>
+          <t>Aruba S.p.A.</t>
+        </is>
+      </c>
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>Sovranità digitale: infrastrutture, energia e regole nella strategia di Aruba</t>
+        </is>
+      </c>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E49" s="19" t="inlineStr">
+        <is>
+          <t>Aruba delinea la propria strategia 2026 su cloud sovrano, infrastrutture e sostenibilità energetica, con AI come elemento strutturale delle operazioni.</t>
+        </is>
+      </c>
+      <c r="F49" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G49" s="19" t="inlineStr">
         <is>
           <t>🆕 Sì</t>
         </is>
@@ -2747,6 +2932,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F42" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F43" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F44" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F45" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F46" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F47" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F48" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F49" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/files/telco_b2b_monitor.xlsx
+++ b/files/telco_b2b_monitor.xlsx
@@ -1090,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4582,6 +4582,191 @@
         </is>
       </c>
       <c r="G95" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="36" customHeight="1">
+      <c r="A96" s="19" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone</t>
+        </is>
+      </c>
+      <c r="C96" s="20" t="inlineStr">
+        <is>
+          <t>Fastweb + Vodafone entra in TM Forum, l'alleanza globale dell'ecosistema Tlc</t>
+        </is>
+      </c>
+      <c r="D96" s="19" t="inlineStr">
+        <is>
+          <t>Generale</t>
+        </is>
+      </c>
+      <c r="E96" s="19" t="inlineStr">
+        <is>
+          <t>La partecipazione al TM Forum consente a Fastweb + Vodafone di sperimentare tecnologie all'avanguardia in un ambiente sicuro, ottimizzando risorse e partecipando alla definizione degli standard globali delle telecomunicazioni.</t>
+        </is>
+      </c>
+      <c r="F96" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G96" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="36" customHeight="1">
+      <c r="A97" s="19" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone</t>
+        </is>
+      </c>
+      <c r="C97" s="20" t="inlineStr">
+        <is>
+          <t>Rimodulazioni Fastweb per mobile e rete fissa da aprile 2026</t>
+        </is>
+      </c>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t>Generale</t>
+        </is>
+      </c>
+      <c r="E97" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb annuncia rimodulazioni delle tariffe per clienti mobile e rete fissa a partire da aprile 2026, con possibilità di recesso senza costi aggiuntivi.</t>
+        </is>
+      </c>
+      <c r="F97" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G97" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="36" customHeight="1">
+      <c r="A98" s="19" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="19" t="inlineStr">
+        <is>
+          <t>Aruba S.p.A.</t>
+        </is>
+      </c>
+      <c r="C98" s="20" t="inlineStr">
+        <is>
+          <t>Aruba Cloud VPS con AI preinstallata: offerta per testare agenti IA enterprise</t>
+        </is>
+      </c>
+      <c r="D98" s="19" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E98" s="19" t="inlineStr">
+        <is>
+          <t>Aruba Cloud lancia VPS con AI agent preinstallato, offrendo una gamma da 1 core/1GB RAM a 16 core/32GB RAM, sia Linux che Windows, pensati per aziende che vogliono sperimentare soluzioni IA in cloud in modo semplice.</t>
+        </is>
+      </c>
+      <c r="F98" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G98" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="36" customHeight="1">
+      <c r="A99" s="19" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="19" t="inlineStr">
+        <is>
+          <t>Scaleway</t>
+        </is>
+      </c>
+      <c r="C99" s="20" t="inlineStr">
+        <is>
+          <t>Scaleway L40S-4-48G GPU Cloud Plan disponibile ad aprile 2026</t>
+        </is>
+      </c>
+      <c r="D99" s="19" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E99" s="19" t="inlineStr">
+        <is>
+          <t>Scaleway rende disponibile il piano L40S-4-48G per GPU cloud computing ad EUR 4.088/mese su piattaforma Linux, ampliando l'offerta di infrastrutture AI/ML ad alte prestazioni.</t>
+        </is>
+      </c>
+      <c r="F99" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G99" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="36" customHeight="1">
+      <c r="A100" s="19" t="inlineStr">
+        <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone</t>
+        </is>
+      </c>
+      <c r="C100" s="20" t="inlineStr">
+        <is>
+          <t>Il marchio Vodafone sparirà in Italia: nuovo brand in arrivo entro il 2029</t>
+        </is>
+      </c>
+      <c r="D100" s="19" t="inlineStr">
+        <is>
+          <t>Generale</t>
+        </is>
+      </c>
+      <c r="E100" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb S.p.A. potrà utilizzare il marchio Vodafone solo in licenza fino al 2029. È in corso la definizione di un nuovo brand che sostituirà Vodafone in Italia per il mercato consumer e B2B.</t>
+        </is>
+      </c>
+      <c r="F100" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G100" s="19" t="inlineStr">
         <is>
           <t>🆕 Sì</t>
         </is>
@@ -4685,6 +4870,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F93" r:id="rId91"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F94" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F95" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F96" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F97" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId98"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/files/telco_b2b_monitor.xlsx
+++ b/files/telco_b2b_monitor.xlsx
@@ -1090,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G100"/>
+  <dimension ref="A1:G102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4767,6 +4767,80 @@
         </is>
       </c>
       <c r="G100" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="36" customHeight="1">
+      <c r="A101" s="19" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone</t>
+        </is>
+      </c>
+      <c r="C101" s="20" t="inlineStr">
+        <is>
+          <t>Fastweb + Vodafone aderisce a TM Forum e rafforza il lavoro su AI, standard aperti e reti autonome</t>
+        </is>
+      </c>
+      <c r="D101" s="19" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E101" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb SpA e Vodafone Shared Operations Limited hanno aderito al TM Forum (data adesione 7 aprile 2026), network internazionale che riunisce i principali operatori e player tecnologici del settore. L'adesione consentirà di sperimentare tecnologie all'avanguardia, partecipare alla definizione di standard e progettare le tendenze future del settore telco globale, con focus su AI, standard aperti e reti autonome.</t>
+        </is>
+      </c>
+      <c r="F101" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G101" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="36" customHeight="1">
+      <c r="A102" s="19" t="inlineStr">
+        <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="19" t="inlineStr">
+        <is>
+          <t>Scaleway</t>
+        </is>
+      </c>
+      <c r="C102" s="20" t="inlineStr">
+        <is>
+          <t>Scaleway: piano GPU L40S-4-48G disponibile per workload AI/Cloud ad alte prestazioni</t>
+        </is>
+      </c>
+      <c r="D102" s="19" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E102" s="19" t="inlineStr">
+        <is>
+          <t>Scaleway ha reso disponibile il piano L40S-4-48G, istanza GPU cloud basata su NVIDIA L40S con 48GB VRAM, a partire da EUR 4.088,00/mese, ottimizzato per carichi di lavoro AI e machine learning ad alte prestazioni. Listino aggiornato ad aprile 2026.</t>
+        </is>
+      </c>
+      <c r="F102" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G102" s="19" t="inlineStr">
         <is>
           <t>🆕 Sì</t>
         </is>
@@ -4875,6 +4949,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F98" r:id="rId96"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F99" r:id="rId97"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId100"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/files/telco_b2b_monitor.xlsx
+++ b/files/telco_b2b_monitor.xlsx
@@ -1090,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G102"/>
+  <dimension ref="A1:G107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4841,6 +4841,191 @@
         </is>
       </c>
       <c r="G102" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="36" customHeight="1">
+      <c r="A103" s="19" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone</t>
+        </is>
+      </c>
+      <c r="C103" s="20" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone aderisce a TM Forum e rafforza il lavoro su AI, standard aperti e reti autonome</t>
+        </is>
+      </c>
+      <c r="D103" s="19" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E103" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb SpA e Vodafone Shared Operations Limited entrano ufficialmente in TM Forum (data di adesione: 7 aprile 2026), l'alleanza globale di oltre 800 aziende telco e tech. Il focus è su AI-native networks, reti autonome di livello 4 (analisi predittiva, gestione chiusa dei processi), Composable IT/BSS-OSS interoperabili e Open Digital Architecture. L'adesione abilita l'accesso a tavoli di sviluppo su API aperte e standard condivisi.</t>
+        </is>
+      </c>
+      <c r="F103" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G103" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="36" customHeight="1">
+      <c r="A104" s="19" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="19" t="inlineStr">
+        <is>
+          <t>Aruba S.p.A.</t>
+        </is>
+      </c>
+      <c r="C104" s="20" t="inlineStr">
+        <is>
+          <t>Aruba Cloud lancia VPS con AI (OpenClaw preinstallato) per aziende e sviluppatori</t>
+        </is>
+      </c>
+      <c r="D104" s="19" t="inlineStr">
+        <is>
+          <t>Cloud</t>
+        </is>
+      </c>
+      <c r="E104" s="19" t="inlineStr">
+        <is>
+          <t>Aruba ha lanciato una nuova offerta di VPS Cloud con OpenClaw AI Agent preinstallato, rivolta ad aziende e sviluppatori che vogliono sperimentare agenti AI autonomi su infrastruttura cloud europea. L'offerta riduce le barriere di adozione e si inserisce nella crescita esplosiva del progetto (oltre 300.000 stelle GitHub, acquisito da OpenAI a febbraio 2026). Pricing base: VPS 4 vCPU / 8 GB RAM da ~26-38 €/mese.</t>
+        </is>
+      </c>
+      <c r="F104" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G104" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="36" customHeight="1">
+      <c r="A105" s="19" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="19" t="inlineStr">
+        <is>
+          <t>Tessellis/Tiscali</t>
+        </is>
+      </c>
+      <c r="C105" s="20" t="inlineStr">
+        <is>
+          <t>Tiscali lancia offerta convergente Casa Home Safe + Mobile 200 Pro (4G) a 33,80 €/mese</t>
+        </is>
+      </c>
+      <c r="D105" s="19" t="inlineStr">
+        <is>
+          <t>Generale</t>
+        </is>
+      </c>
+      <c r="E105" s="19" t="inlineStr">
+        <is>
+          <t>Dal 9 aprile 2026 Tiscali arricchisce il portafoglio convergente fisso+mobile con la nuova Casa Home Safe + Mobile 200 Pro in 4G, abbinata alla linea fissa a 23,90 €/mese. L'offerta affianca la versione 5G (Mobile 350 Pro) e include minuti illimitati, 100 SMS e 200 GB dati in 4G. Il costo complessivo è 33,80 €/mese a tempo indeterminato.</t>
+        </is>
+      </c>
+      <c r="F105" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G105" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="36" customHeight="1">
+      <c r="A106" s="19" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="19" t="inlineStr">
+        <is>
+          <t>Iliad Business</t>
+        </is>
+      </c>
+      <c r="C106" s="20" t="inlineStr">
+        <is>
+          <t>Iliad lancia Top 170 Plus a 7,99 €/mese con Giga Extra in roaming UE</t>
+        </is>
+      </c>
+      <c r="D106" s="19" t="inlineStr">
+        <is>
+          <t>Generale</t>
+        </is>
+      </c>
+      <c r="E106" s="19" t="inlineStr">
+        <is>
+          <t>Dal 2 aprile 2026 Iliad propone la nuova offerta Top 170 Plus a 7,99 €/mese, disponibile per nuovi clienti e già clienti fino al 19 maggio 2026. Include 170 GB dati in 5G (dove disponibile), minuti e SMS illimitati, e Giga Extra in roaming UE. Nessun vincolo né costo di disattivazione.</t>
+        </is>
+      </c>
+      <c r="F106" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G106" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="36" customHeight="1">
+      <c r="A107" s="19" t="inlineStr">
+        <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="19" t="inlineStr">
+        <is>
+          <t>Scaleway</t>
+        </is>
+      </c>
+      <c r="C107" s="20" t="inlineStr">
+        <is>
+          <t>Scaleway lancia L40S-4-48G: istanza GPU cloud con 4x NVIDIA L40S per AI e rendering</t>
+        </is>
+      </c>
+      <c r="D107" s="19" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E107" s="19" t="inlineStr">
+        <is>
+          <t>Dal 5 aprile 2026 Scaleway rende disponibile il piano L40S-4-48G: 32 vCPU, 384 GB RAM, 4 GPU NVIDIA L40S, ~4.088 €/mese pay-as-you-go. Compatibile con Kubernetes e integrato nell'ecosistema Scaleway, è progettato per AI training, inference, rendering e workload accelerati in cloud europeo (datacenter FR/PL, targeting IT incluso). Parte della linea L40S GPU Instances.</t>
+        </is>
+      </c>
+      <c r="F107" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G107" s="19" t="inlineStr">
         <is>
           <t>🆕 Sì</t>
         </is>
@@ -4951,6 +5136,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F100" r:id="rId98"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F101" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F102" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F103" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F104" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId105"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/files/telco_b2b_monitor.xlsx
+++ b/files/telco_b2b_monitor.xlsx
@@ -1090,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G107"/>
+  <dimension ref="A1:G108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5026,6 +5026,43 @@
         </is>
       </c>
       <c r="G107" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="36" customHeight="1">
+      <c r="A108" s="19" t="inlineStr">
+        <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="19" t="inlineStr">
+        <is>
+          <t>Retelit</t>
+        </is>
+      </c>
+      <c r="C108" s="20" t="inlineStr">
+        <is>
+          <t>Via libera UE a MEF e Retelit per l'acquisizione di Sparkle da TIM</t>
+        </is>
+      </c>
+      <c r="D108" s="19" t="inlineStr">
+        <is>
+          <t>Generale</t>
+        </is>
+      </c>
+      <c r="E108" s="19" t="inlineStr">
+        <is>
+          <t>La Commissione Europea ha approvato l'acquisizione di TIM Sparkle da parte di Retelit e del Ministero dell'Economia e delle Finanze, operazione registrata nell'Antitrust europeo il 10 aprile 2026.</t>
+        </is>
+      </c>
+      <c r="F108" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G108" s="19" t="inlineStr">
         <is>
           <t>🆕 Sì</t>
         </is>
@@ -5141,6 +5178,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F105" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId106"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/files/telco_b2b_monitor.xlsx
+++ b/files/telco_b2b_monitor.xlsx
@@ -1090,7 +1090,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G108"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -5063,6 +5063,80 @@
         </is>
       </c>
       <c r="G108" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="36" customHeight="1">
+      <c r="A109" s="19" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="19" t="inlineStr">
+        <is>
+          <t>TIM Enterprise</t>
+        </is>
+      </c>
+      <c r="C109" s="20" t="inlineStr">
+        <is>
+          <t>Poste-Tim, Del Fante: ampliamo base clienti e offerta tech</t>
+        </is>
+      </c>
+      <c r="D109" s="19" t="inlineStr">
+        <is>
+          <t>Generale</t>
+        </is>
+      </c>
+      <c r="E109" s="19" t="inlineStr">
+        <is>
+          <t>OPAS Poste su TIM notificata al governo. Del Fante difende l'operazione e punta su sinergie, nuovi clienti e sviluppo dell'offerta tecnologica enterprise.</t>
+        </is>
+      </c>
+      <c r="F109" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G109" s="19" t="inlineStr">
+        <is>
+          <t>🆕 Sì</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="36" customHeight="1">
+      <c r="A110" s="19" t="inlineStr">
+        <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb+Vodafone</t>
+        </is>
+      </c>
+      <c r="C110" s="20" t="inlineStr">
+        <is>
+          <t>Fastweb + Vodafone entra in TM Forum: cosa cambia per le reti</t>
+        </is>
+      </c>
+      <c r="D110" s="19" t="inlineStr">
+        <is>
+          <t>AI</t>
+        </is>
+      </c>
+      <c r="E110" s="19" t="inlineStr">
+        <is>
+          <t>Fastweb + Vodafone aderisce a TM Forum (7 aprile 2026) per lavorare su automazione, AI, standard aperti e reti autonome con oltre 800 aziende globali del settore TLC.</t>
+        </is>
+      </c>
+      <c r="F110" s="21" t="inlineStr">
+        <is>
+          <t>→ Fonte</t>
+        </is>
+      </c>
+      <c r="G110" s="19" t="inlineStr">
         <is>
           <t>🆕 Sì</t>
         </is>
@@ -5179,6 +5253,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F106" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F107" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F108" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F109" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F110" r:id="rId108"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
